--- a/Database of rubberized concrete and its compressive strength.xlsx
+++ b/Database of rubberized concrete and its compressive strength.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\changzhou\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\changzhou\Desktop\SCI-10 MTC\1 Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC00B8EE-3DF9-45ED-BDDF-E291549432AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{390D9CED-72CA-4CDE-B847-7D986F5007BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{811D10FA-E496-478A-BA95-EB77FE6E0337}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="39">
   <si>
     <t>w/c</t>
   </si>
@@ -93,14 +93,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>100*100*100</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>150*150*150</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Xue 2022</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -150,10 +142,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>MPa (150cubic)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>MPa (original)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -182,6 +170,63 @@
     <t>rubber</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t xml:space="preserve">Specimen Size </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>100mm*100mm*100mm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Specimen size</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>150mm*150mm*150mm</t>
+  </si>
+  <si>
+    <t>MPa (150mm cubic)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Testing standard</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BS1881:Part116:1983</t>
+  </si>
+  <si>
+    <t>ASTM C39</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>GB/T50081</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>2002</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -190,9 +235,9 @@
   <numFmts count="3">
     <numFmt numFmtId="176" formatCode="0.0"/>
     <numFmt numFmtId="177" formatCode="0.0_);[Red]\(0.0\)"/>
-    <numFmt numFmtId="180" formatCode="0.00000"/>
+    <numFmt numFmtId="178" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -218,6 +263,36 @@
       <vertAlign val="superscript"/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <family val="1"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
@@ -262,7 +337,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -312,18 +387,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -644,13 +722,17 @@
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="3" max="4" width="8.77734375" customWidth="1"/>
-    <col min="5" max="5" width="13.88671875" customWidth="1"/>
-    <col min="6" max="6" width="16.44140625" customWidth="1"/>
-    <col min="7" max="7" width="16.6640625" customWidth="1"/>
-    <col min="8" max="8" width="16.88671875" customWidth="1"/>
-    <col min="9" max="9" width="16.77734375" customWidth="1"/>
-    <col min="11" max="12" width="19.6640625" customWidth="1"/>
+    <col min="2" max="2" width="7.88671875" customWidth="1"/>
+    <col min="3" max="3" width="7.77734375" customWidth="1"/>
+    <col min="4" max="4" width="7.33203125" customWidth="1"/>
+    <col min="5" max="5" width="9.6640625" customWidth="1"/>
+    <col min="6" max="6" width="12.77734375" customWidth="1"/>
+    <col min="7" max="7" width="13.88671875" customWidth="1"/>
+    <col min="8" max="8" width="14.77734375" customWidth="1"/>
+    <col min="9" max="9" width="13.6640625" customWidth="1"/>
+    <col min="10" max="10" width="6.88671875" customWidth="1"/>
+    <col min="11" max="11" width="18.109375" customWidth="1"/>
+    <col min="12" max="12" width="18.6640625" customWidth="1"/>
     <col min="14" max="17" width="9" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="9.77734375" bestFit="1" customWidth="1"/>
     <col min="19" max="20" width="10.77734375" bestFit="1" customWidth="1"/>
@@ -663,10 +745,10 @@
       <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="D1" s="16"/>
+      <c r="C1" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1" s="18"/>
       <c r="E1" s="3" t="s">
         <v>1</v>
       </c>
@@ -701,34 +783,34 @@
         <v>6</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>10</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>2</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>12</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="L2" s="7" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
@@ -736,7 +818,7 @@
     </row>
     <row r="3" spans="1:15" ht="14.4" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B3" s="5">
         <v>0.35</v>
@@ -817,8 +899,8 @@
       <c r="O4" s="1"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>17</v>
+      <c r="A5" s="19" t="s">
+        <v>30</v>
       </c>
       <c r="B5" s="3">
         <v>0.35</v>
@@ -859,7 +941,9 @@
       <c r="O5" s="1"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="1"/>
+      <c r="A6" s="19" t="s">
+        <v>31</v>
+      </c>
       <c r="B6" s="3">
         <v>0.35</v>
       </c>
@@ -899,9 +983,7 @@
       <c r="O6" s="1"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>22</v>
-      </c>
+      <c r="A7" s="20"/>
       <c r="B7" s="3">
         <v>0.4</v>
       </c>
@@ -941,6 +1023,9 @@
       <c r="O7" s="1"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" s="19" t="s">
+        <v>35</v>
+      </c>
       <c r="B8" s="3">
         <v>0.4</v>
       </c>
@@ -980,6 +1065,9 @@
       <c r="O8" s="1"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9" s="19" t="s">
+        <v>38</v>
+      </c>
       <c r="B9" s="3">
         <v>0.4</v>
       </c>
@@ -1019,6 +1107,7 @@
       <c r="O9" s="1"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10" s="19"/>
       <c r="B10" s="3">
         <v>0.4</v>
       </c>
@@ -1058,7 +1147,9 @@
       <c r="O10" s="1"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="1"/>
+      <c r="A11" s="19" t="s">
+        <v>20</v>
+      </c>
       <c r="B11" s="3">
         <v>0.45</v>
       </c>
@@ -1098,7 +1189,6 @@
       <c r="O11" s="1"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="1"/>
       <c r="B12" s="3">
         <v>0.45</v>
       </c>
@@ -1138,7 +1228,6 @@
       <c r="O12" s="1"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
       <c r="B13" s="3">
         <v>0.45</v>
       </c>
@@ -1300,8 +1389,8 @@
       <c r="O16" s="1"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>17</v>
+      <c r="A17" s="19" t="s">
+        <v>30</v>
       </c>
       <c r="B17" s="3">
         <v>0.53</v>
@@ -1342,7 +1431,9 @@
       <c r="O17" s="1"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18" s="1"/>
+      <c r="A18" s="19" t="s">
+        <v>31</v>
+      </c>
       <c r="B18" s="3">
         <v>0.53</v>
       </c>
@@ -1382,9 +1473,7 @@
       <c r="O18" s="1"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>22</v>
-      </c>
+      <c r="A19" s="20"/>
       <c r="B19" s="3">
         <v>0.53</v>
       </c>
@@ -1424,6 +1513,9 @@
       <c r="O19" s="1"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A20" s="19" t="s">
+        <v>35</v>
+      </c>
       <c r="B20" s="3">
         <v>0.53</v>
       </c>
@@ -1463,7 +1555,9 @@
       <c r="O20" s="1"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" s="1"/>
+      <c r="A21" s="19" t="s">
+        <v>38</v>
+      </c>
       <c r="B21" s="3">
         <v>0.53</v>
       </c>
@@ -1503,7 +1597,7 @@
       <c r="O21" s="1"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="1"/>
+      <c r="A22" s="19"/>
       <c r="B22" s="3">
         <v>0.53</v>
       </c>
@@ -1543,7 +1637,9 @@
       <c r="O22" s="1"/>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A23" s="1"/>
+      <c r="A23" s="19" t="s">
+        <v>20</v>
+      </c>
       <c r="B23" s="3">
         <v>0.53</v>
       </c>
@@ -1583,7 +1679,6 @@
       <c r="O23" s="1"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A24" s="1"/>
       <c r="B24" s="3">
         <v>0.53</v>
       </c>
@@ -1623,7 +1718,6 @@
       <c r="O24" s="1"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A25" s="1"/>
       <c r="B25" s="3">
         <v>0.53</v>
       </c>
@@ -2145,8 +2239,8 @@
       <c r="O37" s="1"/>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>17</v>
+      <c r="A38" s="19" t="s">
+        <v>30</v>
       </c>
       <c r="B38" s="3">
         <v>0.41</v>
@@ -2187,7 +2281,9 @@
       <c r="O38" s="1"/>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A39" s="1"/>
+      <c r="A39" s="19" t="s">
+        <v>31</v>
+      </c>
       <c r="B39" s="3">
         <v>0.41</v>
       </c>
@@ -2227,9 +2323,7 @@
       <c r="O39" s="1"/>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>22</v>
-      </c>
+      <c r="A40" s="20"/>
       <c r="B40" s="3">
         <v>0.41</v>
       </c>
@@ -2269,6 +2363,9 @@
       <c r="O40" s="1"/>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A41" s="19" t="s">
+        <v>35</v>
+      </c>
       <c r="B41" s="3">
         <v>0.56999999999999995</v>
       </c>
@@ -2308,7 +2405,9 @@
       <c r="O41" s="1"/>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A42" s="1"/>
+      <c r="A42" s="19" t="s">
+        <v>36</v>
+      </c>
       <c r="B42" s="3">
         <v>0.56999999999999995</v>
       </c>
@@ -2348,7 +2447,7 @@
       <c r="O42" s="1"/>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A43" s="1"/>
+      <c r="A43" s="19"/>
       <c r="B43" s="3">
         <v>0.56999999999999995</v>
       </c>
@@ -2388,7 +2487,9 @@
       <c r="O43" s="1"/>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A44" s="1"/>
+      <c r="A44" s="19" t="s">
+        <v>20</v>
+      </c>
       <c r="B44" s="3">
         <v>0.56999999999999995</v>
       </c>
@@ -2428,7 +2529,6 @@
       <c r="O44" s="1"/>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A45" s="1"/>
       <c r="B45" s="3">
         <v>0.56999999999999995</v>
       </c>
@@ -2468,7 +2568,6 @@
       <c r="O45" s="1"/>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A46" s="1"/>
       <c r="B46" s="3">
         <v>0.68</v>
       </c>
@@ -3864,26 +3963,26 @@
         <v>15.814</v>
       </c>
       <c r="M80" s="1"/>
-      <c r="N80" s="17" t="s">
+      <c r="N80" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="O80" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="P80" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q80" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="O80" s="17" t="s">
+      <c r="R80" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="P80" s="18" t="s">
+      <c r="S80" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="Q80" s="18" t="s">
+      <c r="T80" s="16" t="s">
         <v>28</v>
-      </c>
-      <c r="R80" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="S80" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="T80" s="18" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="81" spans="1:20" ht="14.4" thickTop="1" x14ac:dyDescent="0.25">
@@ -3924,25 +4023,25 @@
         <v>75.8</v>
       </c>
       <c r="M81" s="1"/>
-      <c r="N81" s="19">
+      <c r="N81" s="17">
         <v>0.2625954198473282</v>
       </c>
-      <c r="O81" s="19">
+      <c r="O81" s="17">
         <v>0.39333333333333331</v>
       </c>
-      <c r="P81" s="20">
-        <v>0</v>
-      </c>
-      <c r="Q81" s="20">
-        <v>0</v>
-      </c>
-      <c r="R81" s="20">
-        <v>0</v>
-      </c>
-      <c r="S81" s="20">
-        <v>0</v>
-      </c>
-      <c r="T81" s="20">
+      <c r="P81" s="17">
+        <v>0</v>
+      </c>
+      <c r="Q81" s="17">
+        <v>0</v>
+      </c>
+      <c r="R81" s="17">
+        <v>0</v>
+      </c>
+      <c r="S81" s="17">
+        <v>0</v>
+      </c>
+      <c r="T81" s="17">
         <v>0</v>
       </c>
     </row>
@@ -3982,31 +4081,31 @@
         <v>81</v>
       </c>
       <c r="M82" s="1"/>
-      <c r="N82" s="19">
+      <c r="N82" s="17">
         <v>0.26145038167938928</v>
       </c>
-      <c r="O82" s="19">
+      <c r="O82" s="17">
         <v>0.39185185185185184</v>
       </c>
-      <c r="P82" s="20">
-        <v>0</v>
-      </c>
-      <c r="Q82" s="20">
-        <v>0</v>
-      </c>
-      <c r="R82" s="20">
-        <v>0</v>
-      </c>
-      <c r="S82" s="20">
-        <v>0</v>
-      </c>
-      <c r="T82" s="20">
+      <c r="P82" s="17">
+        <v>0</v>
+      </c>
+      <c r="Q82" s="17">
+        <v>0</v>
+      </c>
+      <c r="R82" s="17">
+        <v>0</v>
+      </c>
+      <c r="S82" s="17">
+        <v>0</v>
+      </c>
+      <c r="T82" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A83" s="1" t="s">
-        <v>18</v>
+      <c r="A83" s="21" t="s">
+        <v>32</v>
       </c>
       <c r="B83" s="3">
         <v>0.4</v>
@@ -4042,30 +4141,32 @@
         <v>82.7</v>
       </c>
       <c r="M83" s="1"/>
-      <c r="N83" s="19">
+      <c r="N83" s="17">
         <v>0.26030534351145035</v>
       </c>
-      <c r="O83" s="19">
+      <c r="O83" s="17">
         <v>0.39037037037037031</v>
       </c>
-      <c r="P83" s="20">
-        <v>0</v>
-      </c>
-      <c r="Q83" s="20">
-        <v>0</v>
-      </c>
-      <c r="R83" s="20">
-        <v>0</v>
-      </c>
-      <c r="S83" s="20">
-        <v>0</v>
-      </c>
-      <c r="T83" s="20">
+      <c r="P83" s="17">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="17">
+        <v>0</v>
+      </c>
+      <c r="R83" s="17">
+        <v>0</v>
+      </c>
+      <c r="S83" s="17">
+        <v>0</v>
+      </c>
+      <c r="T83" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A84" s="1"/>
+      <c r="A84" s="21" t="s">
+        <v>33</v>
+      </c>
       <c r="B84" s="3">
         <v>0.4</v>
       </c>
@@ -4100,30 +4201,30 @@
         <v>84</v>
       </c>
       <c r="M84" s="1"/>
-      <c r="N84" s="19">
+      <c r="N84" s="17">
         <v>0.25954198473282442</v>
       </c>
-      <c r="O84" s="19">
+      <c r="O84" s="17">
         <v>0.38851851851851849</v>
       </c>
-      <c r="P84" s="20">
-        <v>0</v>
-      </c>
-      <c r="Q84" s="20">
-        <v>0</v>
-      </c>
-      <c r="R84" s="20">
-        <v>0</v>
-      </c>
-      <c r="S84" s="20">
-        <v>0</v>
-      </c>
-      <c r="T84" s="20">
+      <c r="P84" s="17">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="17">
+        <v>0</v>
+      </c>
+      <c r="R84" s="17">
+        <v>0</v>
+      </c>
+      <c r="S84" s="17">
+        <v>0</v>
+      </c>
+      <c r="T84" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A85" s="1"/>
+      <c r="A85" s="21"/>
       <c r="B85" s="3">
         <v>0.4</v>
       </c>
@@ -4158,29 +4259,32 @@
         <v>85.7</v>
       </c>
       <c r="M85" s="1"/>
-      <c r="N85" s="19">
+      <c r="N85" s="17">
         <v>0.25839694656488549</v>
       </c>
-      <c r="O85" s="19">
+      <c r="O85" s="17">
         <v>0.38703703703703701</v>
       </c>
-      <c r="P85" s="20">
-        <v>0</v>
-      </c>
-      <c r="Q85" s="20">
-        <v>0</v>
-      </c>
-      <c r="R85" s="20">
-        <v>0</v>
-      </c>
-      <c r="S85" s="20">
-        <v>0</v>
-      </c>
-      <c r="T85" s="20">
+      <c r="P85" s="17">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="17">
+        <v>0</v>
+      </c>
+      <c r="R85" s="17">
+        <v>0</v>
+      </c>
+      <c r="S85" s="17">
+        <v>0</v>
+      </c>
+      <c r="T85" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A86" s="21" t="s">
+        <v>35</v>
+      </c>
       <c r="B86" s="3">
         <v>0.4</v>
       </c>
@@ -4215,30 +4319,32 @@
         <v>70.400000000000006</v>
       </c>
       <c r="M86" s="1"/>
-      <c r="N86" s="19">
+      <c r="N86" s="17">
         <v>0.2625954198473282</v>
       </c>
-      <c r="O86" s="19">
+      <c r="O86" s="17">
         <v>0.39333333333333331</v>
       </c>
-      <c r="P86" s="20">
+      <c r="P86" s="17">
         <v>3.2824427480916026E-3</v>
       </c>
-      <c r="Q86" s="20">
+      <c r="Q86" s="17">
         <v>4.9166666666666664E-3</v>
       </c>
-      <c r="R86" s="20">
+      <c r="R86" s="17">
         <v>2.72442748091603</v>
       </c>
-      <c r="S86" s="20">
+      <c r="S86" s="17">
         <v>5.0149999999999997</v>
       </c>
-      <c r="T86" s="20">
+      <c r="T86" s="17">
         <v>7.7394274809160297</v>
       </c>
     </row>
     <row r="87" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A87" s="1"/>
+      <c r="A87" s="21" t="s">
+        <v>37</v>
+      </c>
       <c r="B87" s="3">
         <v>0.4</v>
       </c>
@@ -4273,25 +4379,25 @@
         <v>72.5</v>
       </c>
       <c r="M87" s="1"/>
-      <c r="N87" s="19">
+      <c r="N87" s="17">
         <v>0.26145038167938928</v>
       </c>
-      <c r="O87" s="19">
+      <c r="O87" s="17">
         <v>0.39185185185185184</v>
       </c>
-      <c r="P87" s="20">
+      <c r="P87" s="17">
         <v>3.2681297709923661E-3</v>
       </c>
-      <c r="Q87" s="20">
+      <c r="Q87" s="17">
         <v>4.898148148148148E-3</v>
       </c>
-      <c r="R87" s="20">
+      <c r="R87" s="17">
         <v>2.7125477099236637</v>
       </c>
-      <c r="S87" s="20">
+      <c r="S87" s="17">
         <v>4.9961111111111105</v>
       </c>
-      <c r="T87" s="20">
+      <c r="T87" s="17">
         <v>7.7086588210347742</v>
       </c>
     </row>
@@ -4331,25 +4437,25 @@
         <v>75.400000000000006</v>
       </c>
       <c r="M88" s="1"/>
-      <c r="N88" s="19">
+      <c r="N88" s="17">
         <v>0.26030534351145035</v>
       </c>
-      <c r="O88" s="19">
+      <c r="O88" s="17">
         <v>0.39037037037037031</v>
       </c>
-      <c r="P88" s="20">
+      <c r="P88" s="17">
         <v>3.2538167938931297E-3</v>
       </c>
-      <c r="Q88" s="20">
+      <c r="Q88" s="17">
         <v>4.8796296296296287E-3</v>
       </c>
-      <c r="R88" s="20">
+      <c r="R88" s="17">
         <v>2.7006679389312978</v>
       </c>
-      <c r="S88" s="20">
+      <c r="S88" s="17">
         <v>4.9772222222222213</v>
       </c>
-      <c r="T88" s="20">
+      <c r="T88" s="17">
         <v>7.6778901611535186</v>
       </c>
     </row>
@@ -4389,25 +4495,25 @@
         <v>78.3</v>
       </c>
       <c r="M89" s="1"/>
-      <c r="N89" s="19">
+      <c r="N89" s="17">
         <v>0.25954198473282442</v>
       </c>
-      <c r="O89" s="19">
+      <c r="O89" s="17">
         <v>0.38851851851851849</v>
       </c>
-      <c r="P89" s="20">
+      <c r="P89" s="17">
         <v>3.2442748091603053E-3</v>
       </c>
-      <c r="Q89" s="20">
+      <c r="Q89" s="17">
         <v>4.8564814814814807E-3</v>
       </c>
-      <c r="R89" s="20">
+      <c r="R89" s="17">
         <v>2.6927480916030531</v>
       </c>
-      <c r="S89" s="20">
+      <c r="S89" s="17">
         <v>4.9536111111111101</v>
       </c>
-      <c r="T89" s="20">
+      <c r="T89" s="17">
         <v>7.6463592027141631</v>
       </c>
     </row>
@@ -4447,25 +4553,25 @@
         <v>79.099999999999994</v>
       </c>
       <c r="M90" s="1"/>
-      <c r="N90" s="19">
+      <c r="N90" s="17">
         <v>0.25839694656488549</v>
       </c>
-      <c r="O90" s="19">
+      <c r="O90" s="17">
         <v>0.38703703703703701</v>
       </c>
-      <c r="P90" s="20">
+      <c r="P90" s="17">
         <v>3.2299618320610684E-3</v>
       </c>
-      <c r="Q90" s="20">
+      <c r="Q90" s="17">
         <v>4.8379629629629632E-3</v>
       </c>
-      <c r="R90" s="20">
+      <c r="R90" s="17">
         <v>2.6808683206106867</v>
       </c>
-      <c r="S90" s="20">
+      <c r="S90" s="17">
         <v>4.9347222222222227</v>
       </c>
-      <c r="T90" s="20">
+      <c r="T90" s="17">
         <v>7.6155905428329094</v>
       </c>
     </row>
@@ -4505,25 +4611,25 @@
         <v>62.8</v>
       </c>
       <c r="M91" s="1"/>
-      <c r="N91" s="19">
+      <c r="N91" s="17">
         <v>0.2625954198473282</v>
       </c>
-      <c r="O91" s="19">
+      <c r="O91" s="17">
         <v>0.39333333333333331</v>
       </c>
-      <c r="P91" s="20">
+      <c r="P91" s="17">
         <v>6.5648854961832051E-3</v>
       </c>
-      <c r="Q91" s="20">
+      <c r="Q91" s="17">
         <v>9.8333333333333328E-3</v>
       </c>
-      <c r="R91" s="20">
+      <c r="R91" s="17">
         <v>5.4488549618320601</v>
       </c>
-      <c r="S91" s="20">
+      <c r="S91" s="17">
         <v>10.029999999999999</v>
       </c>
-      <c r="T91" s="20">
+      <c r="T91" s="17">
         <v>15.478854961832059</v>
       </c>
     </row>
@@ -4563,25 +4669,25 @@
         <v>67.8</v>
       </c>
       <c r="M92" s="1"/>
-      <c r="N92" s="19">
+      <c r="N92" s="17">
         <v>0.26145038167938928</v>
       </c>
-      <c r="O92" s="19">
+      <c r="O92" s="17">
         <v>0.39185185185185184</v>
       </c>
-      <c r="P92" s="20">
+      <c r="P92" s="17">
         <v>6.5362595419847323E-3</v>
       </c>
-      <c r="Q92" s="20">
+      <c r="Q92" s="17">
         <v>9.796296296296296E-3</v>
       </c>
-      <c r="R92" s="20">
+      <c r="R92" s="17">
         <v>5.4250954198473273</v>
       </c>
-      <c r="S92" s="20">
+      <c r="S92" s="17">
         <v>9.992222222222221</v>
       </c>
-      <c r="T92" s="20">
+      <c r="T92" s="17">
         <v>15.417317642069548</v>
       </c>
     </row>
@@ -4621,25 +4727,25 @@
         <v>68.2</v>
       </c>
       <c r="M93" s="1"/>
-      <c r="N93" s="19">
+      <c r="N93" s="17">
         <v>0.26030534351145035</v>
       </c>
-      <c r="O93" s="19">
+      <c r="O93" s="17">
         <v>0.39037037037037031</v>
       </c>
-      <c r="P93" s="20">
+      <c r="P93" s="17">
         <v>6.5076335877862594E-3</v>
       </c>
-      <c r="Q93" s="20">
+      <c r="Q93" s="17">
         <v>9.7592592592592575E-3</v>
       </c>
-      <c r="R93" s="20">
+      <c r="R93" s="17">
         <v>5.4013358778625955</v>
       </c>
-      <c r="S93" s="20">
+      <c r="S93" s="17">
         <v>9.9544444444444427</v>
       </c>
-      <c r="T93" s="20">
+      <c r="T93" s="17">
         <v>15.355780322307037</v>
       </c>
     </row>
@@ -4679,25 +4785,25 @@
         <v>68</v>
       </c>
       <c r="M94" s="1"/>
-      <c r="N94" s="19">
+      <c r="N94" s="17">
         <v>0.25954198473282442</v>
       </c>
-      <c r="O94" s="19">
+      <c r="O94" s="17">
         <v>0.38851851851851849</v>
       </c>
-      <c r="P94" s="20">
+      <c r="P94" s="17">
         <v>6.4885496183206106E-3</v>
       </c>
-      <c r="Q94" s="20">
+      <c r="Q94" s="17">
         <v>9.7129629629629614E-3</v>
       </c>
-      <c r="R94" s="20">
+      <c r="R94" s="17">
         <v>5.3854961832061061</v>
       </c>
-      <c r="S94" s="20">
+      <c r="S94" s="17">
         <v>9.9072222222222202</v>
       </c>
-      <c r="T94" s="20">
+      <c r="T94" s="17">
         <v>15.292718405428326</v>
       </c>
     </row>
@@ -4737,25 +4843,25 @@
         <v>69.400000000000006</v>
       </c>
       <c r="M95" s="1"/>
-      <c r="N95" s="19">
+      <c r="N95" s="17">
         <v>0.25839694656488549</v>
       </c>
-      <c r="O95" s="19">
+      <c r="O95" s="17">
         <v>0.38703703703703701</v>
       </c>
-      <c r="P95" s="20">
+      <c r="P95" s="17">
         <v>6.4599236641221369E-3</v>
       </c>
-      <c r="Q95" s="20">
+      <c r="Q95" s="17">
         <v>9.6759259259259264E-3</v>
       </c>
-      <c r="R95" s="20">
+      <c r="R95" s="17">
         <v>5.3617366412213734</v>
       </c>
-      <c r="S95" s="20">
+      <c r="S95" s="17">
         <v>9.8694444444444454</v>
       </c>
-      <c r="T95" s="20">
+      <c r="T95" s="17">
         <v>15.231181085665819</v>
       </c>
     </row>
@@ -4795,25 +4901,25 @@
         <v>50.7</v>
       </c>
       <c r="M96" s="1"/>
-      <c r="N96" s="19">
+      <c r="N96" s="17">
         <v>0.2625954198473282</v>
       </c>
-      <c r="O96" s="19">
+      <c r="O96" s="17">
         <v>0.39333333333333331</v>
       </c>
-      <c r="P96" s="20">
+      <c r="P96" s="17">
         <v>1.312977099236641E-2</v>
       </c>
-      <c r="Q96" s="20">
+      <c r="Q96" s="17">
         <v>1.9666666666666666E-2</v>
       </c>
-      <c r="R96" s="20">
+      <c r="R96" s="17">
         <v>10.89770992366412</v>
       </c>
-      <c r="S96" s="20">
+      <c r="S96" s="17">
         <v>20.059999999999999</v>
       </c>
-      <c r="T96" s="20">
+      <c r="T96" s="17">
         <v>30.957709923664119</v>
       </c>
     </row>
@@ -4853,25 +4959,25 @@
         <v>55.3</v>
       </c>
       <c r="M97" s="1"/>
-      <c r="N97" s="19">
+      <c r="N97" s="17">
         <v>0.26145038167938928</v>
       </c>
-      <c r="O97" s="19">
+      <c r="O97" s="17">
         <v>0.39185185185185184</v>
       </c>
-      <c r="P97" s="20">
+      <c r="P97" s="17">
         <v>1.3072519083969465E-2</v>
       </c>
-      <c r="Q97" s="20">
+      <c r="Q97" s="17">
         <v>1.9592592592592592E-2</v>
       </c>
-      <c r="R97" s="20">
+      <c r="R97" s="17">
         <v>10.850190839694655</v>
       </c>
-      <c r="S97" s="20">
+      <c r="S97" s="17">
         <v>19.984444444444442</v>
       </c>
-      <c r="T97" s="20">
+      <c r="T97" s="17">
         <v>30.834635284139097</v>
       </c>
     </row>
@@ -4911,25 +5017,25 @@
         <v>56.3</v>
       </c>
       <c r="M98" s="1"/>
-      <c r="N98" s="19">
+      <c r="N98" s="17">
         <v>0.26030534351145035</v>
       </c>
-      <c r="O98" s="19">
+      <c r="O98" s="17">
         <v>0.39037037037037031</v>
       </c>
-      <c r="P98" s="20">
+      <c r="P98" s="17">
         <v>1.3015267175572519E-2</v>
       </c>
-      <c r="Q98" s="20">
+      <c r="Q98" s="17">
         <v>1.9518518518518515E-2</v>
       </c>
-      <c r="R98" s="20">
+      <c r="R98" s="17">
         <v>10.802671755725191</v>
       </c>
-      <c r="S98" s="20">
+      <c r="S98" s="17">
         <v>19.908888888888885</v>
       </c>
-      <c r="T98" s="20">
+      <c r="T98" s="17">
         <v>30.711560644614075</v>
       </c>
     </row>
@@ -4969,25 +5075,25 @@
         <v>55.6</v>
       </c>
       <c r="M99" s="1"/>
-      <c r="N99" s="19">
+      <c r="N99" s="17">
         <v>0.25954198473282442</v>
       </c>
-      <c r="O99" s="19">
+      <c r="O99" s="17">
         <v>0.38851851851851849</v>
       </c>
-      <c r="P99" s="20">
+      <c r="P99" s="17">
         <v>1.2977099236641221E-2</v>
       </c>
-      <c r="Q99" s="20">
+      <c r="Q99" s="17">
         <v>1.9425925925925923E-2</v>
       </c>
-      <c r="R99" s="20">
+      <c r="R99" s="17">
         <v>10.770992366412212</v>
       </c>
-      <c r="S99" s="20">
+      <c r="S99" s="17">
         <v>19.81444444444444</v>
       </c>
-      <c r="T99" s="20">
+      <c r="T99" s="17">
         <v>30.585436810856653</v>
       </c>
     </row>
@@ -5027,25 +5133,25 @@
         <v>61.7</v>
       </c>
       <c r="M100" s="1"/>
-      <c r="N100" s="19">
+      <c r="N100" s="17">
         <v>0.25839694656488549</v>
       </c>
-      <c r="O100" s="19">
+      <c r="O100" s="17">
         <v>0.38703703703703701</v>
       </c>
-      <c r="P100" s="20">
+      <c r="P100" s="17">
         <v>1.2919847328244274E-2</v>
       </c>
-      <c r="Q100" s="20">
+      <c r="Q100" s="17">
         <v>1.9351851851851853E-2</v>
       </c>
-      <c r="R100" s="20">
+      <c r="R100" s="17">
         <v>10.723473282442747</v>
       </c>
-      <c r="S100" s="20">
+      <c r="S100" s="17">
         <v>19.738888888888891</v>
       </c>
-      <c r="T100" s="20">
+      <c r="T100" s="17">
         <v>30.462362171331637</v>
       </c>
     </row>
@@ -5085,25 +5191,25 @@
         <v>40.299999999999997</v>
       </c>
       <c r="M101" s="1"/>
-      <c r="N101" s="19">
+      <c r="N101" s="17">
         <v>0.2625954198473282</v>
       </c>
-      <c r="O101" s="19">
+      <c r="O101" s="17">
         <v>0.39333333333333331</v>
       </c>
-      <c r="P101" s="20">
+      <c r="P101" s="17">
         <v>1.9694656488549615E-2</v>
       </c>
-      <c r="Q101" s="20">
+      <c r="Q101" s="17">
         <v>2.9499999999999998E-2</v>
       </c>
-      <c r="R101" s="20">
+      <c r="R101" s="17">
         <v>16.346564885496182</v>
       </c>
-      <c r="S101" s="20">
+      <c r="S101" s="17">
         <v>30.09</v>
       </c>
-      <c r="T101" s="20">
+      <c r="T101" s="17">
         <v>46.436564885496182</v>
       </c>
     </row>
@@ -5143,25 +5249,25 @@
         <v>44.5</v>
       </c>
       <c r="M102" s="1"/>
-      <c r="N102" s="19">
+      <c r="N102" s="17">
         <v>0.26145038167938928</v>
       </c>
-      <c r="O102" s="19">
+      <c r="O102" s="17">
         <v>0.39185185185185184</v>
       </c>
-      <c r="P102" s="20">
+      <c r="P102" s="17">
         <v>1.9608778625954195E-2</v>
       </c>
-      <c r="Q102" s="20">
+      <c r="Q102" s="17">
         <v>2.9388888888888888E-2</v>
       </c>
-      <c r="R102" s="20">
+      <c r="R102" s="17">
         <v>16.275286259541982</v>
       </c>
-      <c r="S102" s="20">
+      <c r="S102" s="17">
         <v>29.976666666666667</v>
       </c>
-      <c r="T102" s="20">
+      <c r="T102" s="17">
         <v>46.251952926208645</v>
       </c>
     </row>
@@ -5201,25 +5307,25 @@
         <v>45.1</v>
       </c>
       <c r="M103" s="1"/>
-      <c r="N103" s="19">
+      <c r="N103" s="17">
         <v>0.26030534351145035</v>
       </c>
-      <c r="O103" s="19">
+      <c r="O103" s="17">
         <v>0.39037037037037031</v>
       </c>
-      <c r="P103" s="20">
+      <c r="P103" s="17">
         <v>1.9522900763358778E-2</v>
       </c>
-      <c r="Q103" s="20">
+      <c r="Q103" s="17">
         <v>2.9277777777777771E-2</v>
       </c>
-      <c r="R103" s="20">
+      <c r="R103" s="17">
         <v>16.204007633587786</v>
       </c>
-      <c r="S103" s="20">
+      <c r="S103" s="17">
         <v>29.863333333333326</v>
       </c>
-      <c r="T103" s="20">
+      <c r="T103" s="17">
         <v>46.067340966921108</v>
       </c>
     </row>
@@ -5259,25 +5365,25 @@
         <v>46.4</v>
       </c>
       <c r="M104" s="1"/>
-      <c r="N104" s="19">
+      <c r="N104" s="17">
         <v>0.25954198473282442</v>
       </c>
-      <c r="O104" s="19">
+      <c r="O104" s="17">
         <v>0.38851851851851849</v>
       </c>
-      <c r="P104" s="20">
+      <c r="P104" s="17">
         <v>1.9465648854961829E-2</v>
       </c>
-      <c r="Q104" s="20">
+      <c r="Q104" s="17">
         <v>2.9138888888888888E-2</v>
       </c>
-      <c r="R104" s="20">
+      <c r="R104" s="17">
         <v>16.156488549618317</v>
       </c>
-      <c r="S104" s="20">
+      <c r="S104" s="17">
         <v>29.721666666666668</v>
       </c>
-      <c r="T104" s="20">
+      <c r="T104" s="17">
         <v>45.878155216284981</v>
       </c>
     </row>
@@ -5317,25 +5423,25 @@
         <v>47</v>
       </c>
       <c r="M105" s="1"/>
-      <c r="N105" s="19">
+      <c r="N105" s="17">
         <v>0.25839694656488549</v>
       </c>
-      <c r="O105" s="19">
+      <c r="O105" s="17">
         <v>0.38703703703703701</v>
       </c>
-      <c r="P105" s="20">
+      <c r="P105" s="17">
         <v>1.9379770992366412E-2</v>
       </c>
-      <c r="Q105" s="20">
+      <c r="Q105" s="17">
         <v>2.9027777777777777E-2</v>
       </c>
-      <c r="R105" s="20">
+      <c r="R105" s="17">
         <v>16.08520992366412</v>
       </c>
-      <c r="S105" s="20">
+      <c r="S105" s="17">
         <v>29.608333333333334</v>
       </c>
-      <c r="T105" s="20">
+      <c r="T105" s="17">
         <v>45.693543256997458</v>
       </c>
     </row>
@@ -5375,25 +5481,25 @@
         <v>26.4</v>
       </c>
       <c r="M106" s="1"/>
-      <c r="N106" s="19">
+      <c r="N106" s="17">
         <v>0.2625954198473282</v>
       </c>
-      <c r="O106" s="19">
+      <c r="O106" s="17">
         <v>0.39333333333333331</v>
       </c>
-      <c r="P106" s="20">
+      <c r="P106" s="17">
         <v>3.2824427480916026E-2</v>
       </c>
-      <c r="Q106" s="20">
+      <c r="Q106" s="17">
         <v>4.9166666666666664E-2</v>
       </c>
-      <c r="R106" s="20">
+      <c r="R106" s="17">
         <v>27.244274809160299</v>
       </c>
-      <c r="S106" s="20">
+      <c r="S106" s="17">
         <v>50.15</v>
       </c>
-      <c r="T106" s="20">
+      <c r="T106" s="17">
         <v>77.394274809160294</v>
       </c>
     </row>
@@ -5433,25 +5539,25 @@
         <v>29.6</v>
       </c>
       <c r="M107" s="1"/>
-      <c r="N107" s="19">
+      <c r="N107" s="17">
         <v>0.26145038167938928</v>
       </c>
-      <c r="O107" s="19">
+      <c r="O107" s="17">
         <v>0.39185185185185184</v>
       </c>
-      <c r="P107" s="20">
+      <c r="P107" s="17">
         <v>3.268129770992366E-2</v>
       </c>
-      <c r="Q107" s="20">
+      <c r="Q107" s="17">
         <v>4.898148148148148E-2</v>
       </c>
-      <c r="R107" s="20">
+      <c r="R107" s="17">
         <v>27.125477099236633</v>
       </c>
-      <c r="S107" s="20">
+      <c r="S107" s="17">
         <v>49.961111111111109</v>
       </c>
-      <c r="T107" s="20">
+      <c r="T107" s="17">
         <v>77.086588210347742</v>
       </c>
     </row>
@@ -5491,25 +5597,25 @@
         <v>30.5</v>
       </c>
       <c r="M108" s="1"/>
-      <c r="N108" s="19">
+      <c r="N108" s="17">
         <v>0.26030534351145035</v>
       </c>
-      <c r="O108" s="19">
+      <c r="O108" s="17">
         <v>0.39037037037037031</v>
       </c>
-      <c r="P108" s="20">
+      <c r="P108" s="17">
         <v>3.2538167938931294E-2</v>
       </c>
-      <c r="Q108" s="20">
+      <c r="Q108" s="17">
         <v>4.8796296296296289E-2</v>
       </c>
-      <c r="R108" s="20">
+      <c r="R108" s="17">
         <v>27.006679389312971</v>
       </c>
-      <c r="S108" s="20">
+      <c r="S108" s="17">
         <v>49.772222222222219</v>
       </c>
-      <c r="T108" s="20">
+      <c r="T108" s="17">
         <v>76.77890161153519</v>
       </c>
     </row>
@@ -5549,25 +5655,25 @@
         <v>31.8</v>
       </c>
       <c r="M109" s="1"/>
-      <c r="N109" s="19">
+      <c r="N109" s="17">
         <v>0.25954198473282442</v>
       </c>
-      <c r="O109" s="19">
+      <c r="O109" s="17">
         <v>0.38851851851851849</v>
       </c>
-      <c r="P109" s="20">
+      <c r="P109" s="17">
         <v>3.2442748091603052E-2</v>
       </c>
-      <c r="Q109" s="20">
+      <c r="Q109" s="17">
         <v>4.8564814814814811E-2</v>
       </c>
-      <c r="R109" s="20">
+      <c r="R109" s="17">
         <v>26.927480916030532</v>
       </c>
-      <c r="S109" s="20">
+      <c r="S109" s="17">
         <v>49.536111111111104</v>
       </c>
-      <c r="T109" s="20">
+      <c r="T109" s="17">
         <v>76.46359202714163</v>
       </c>
     </row>
@@ -5607,25 +5713,25 @@
         <v>31.8</v>
       </c>
       <c r="M110" s="1"/>
-      <c r="N110" s="19">
+      <c r="N110" s="17">
         <v>0.25839694656488549</v>
       </c>
-      <c r="O110" s="19">
+      <c r="O110" s="17">
         <v>0.38703703703703701</v>
       </c>
-      <c r="P110" s="20">
+      <c r="P110" s="17">
         <v>3.2299618320610686E-2</v>
       </c>
-      <c r="Q110" s="20">
+      <c r="Q110" s="17">
         <v>4.8379629629629627E-2</v>
       </c>
-      <c r="R110" s="20">
+      <c r="R110" s="17">
         <v>26.808683206106867</v>
       </c>
-      <c r="S110" s="20">
+      <c r="S110" s="17">
         <v>49.347222222222221</v>
       </c>
-      <c r="T110" s="20">
+      <c r="T110" s="17">
         <v>76.155905428329092</v>
       </c>
     </row>
@@ -5665,25 +5771,25 @@
         <v>10.5</v>
       </c>
       <c r="M111" s="1"/>
-      <c r="N111" s="19">
+      <c r="N111" s="17">
         <v>0.2625954198473282</v>
       </c>
-      <c r="O111" s="19">
+      <c r="O111" s="17">
         <v>0.39333333333333331</v>
       </c>
-      <c r="P111" s="20">
+      <c r="P111" s="17">
         <v>6.5648854961832051E-2</v>
       </c>
-      <c r="Q111" s="20">
+      <c r="Q111" s="17">
         <v>9.8333333333333328E-2</v>
       </c>
-      <c r="R111" s="20">
+      <c r="R111" s="17">
         <v>54.488549618320597</v>
       </c>
-      <c r="S111" s="20">
+      <c r="S111" s="17">
         <v>100.3</v>
       </c>
-      <c r="T111" s="20">
+      <c r="T111" s="17">
         <v>154.78854961832059</v>
       </c>
     </row>
@@ -5723,25 +5829,25 @@
         <v>11.2</v>
       </c>
       <c r="M112" s="1"/>
-      <c r="N112" s="19">
+      <c r="N112" s="17">
         <v>0.26145038167938928</v>
       </c>
-      <c r="O112" s="19">
+      <c r="O112" s="17">
         <v>0.39185185185185184</v>
       </c>
-      <c r="P112" s="20">
+      <c r="P112" s="17">
         <v>6.5362595419847319E-2</v>
       </c>
-      <c r="Q112" s="20">
+      <c r="Q112" s="17">
         <v>9.796296296296296E-2</v>
       </c>
-      <c r="R112" s="20">
+      <c r="R112" s="17">
         <v>54.250954198473266</v>
       </c>
-      <c r="S112" s="20">
+      <c r="S112" s="17">
         <v>99.922222222222217</v>
       </c>
-      <c r="T112" s="20">
+      <c r="T112" s="17">
         <v>154.17317642069548</v>
       </c>
     </row>
@@ -5781,25 +5887,25 @@
         <v>11.6</v>
       </c>
       <c r="M113" s="1"/>
-      <c r="N113" s="19">
+      <c r="N113" s="17">
         <v>0.26030534351145035</v>
       </c>
-      <c r="O113" s="19">
+      <c r="O113" s="17">
         <v>0.39037037037037031</v>
       </c>
-      <c r="P113" s="20">
+      <c r="P113" s="17">
         <v>6.5076335877862587E-2</v>
       </c>
-      <c r="Q113" s="20">
+      <c r="Q113" s="17">
         <v>9.7592592592592578E-2</v>
       </c>
-      <c r="R113" s="20">
+      <c r="R113" s="17">
         <v>54.013358778625943</v>
       </c>
-      <c r="S113" s="20">
+      <c r="S113" s="17">
         <v>99.544444444444437</v>
       </c>
-      <c r="T113" s="20">
+      <c r="T113" s="17">
         <v>153.55780322307038</v>
       </c>
     </row>
@@ -5839,25 +5945,25 @@
         <v>11.7</v>
       </c>
       <c r="M114" s="1"/>
-      <c r="N114" s="19">
+      <c r="N114" s="17">
         <v>0.25954198473282442</v>
       </c>
-      <c r="O114" s="19">
+      <c r="O114" s="17">
         <v>0.38851851851851849</v>
       </c>
-      <c r="P114" s="20">
+      <c r="P114" s="17">
         <v>6.4885496183206104E-2</v>
       </c>
-      <c r="Q114" s="20">
+      <c r="Q114" s="17">
         <v>9.7129629629629621E-2</v>
       </c>
-      <c r="R114" s="20">
+      <c r="R114" s="17">
         <v>53.854961832061065</v>
       </c>
-      <c r="S114" s="20">
+      <c r="S114" s="17">
         <v>99.072222222222209</v>
       </c>
-      <c r="T114" s="20">
+      <c r="T114" s="17">
         <v>152.92718405428326</v>
       </c>
     </row>
@@ -5897,25 +6003,25 @@
         <v>11.7</v>
       </c>
       <c r="M115" s="1"/>
-      <c r="N115" s="19">
+      <c r="N115" s="17">
         <v>0.25839694656488549</v>
       </c>
-      <c r="O115" s="19">
+      <c r="O115" s="17">
         <v>0.38703703703703701</v>
       </c>
-      <c r="P115" s="20">
+      <c r="P115" s="17">
         <v>6.4599236641221372E-2</v>
       </c>
-      <c r="Q115" s="20">
+      <c r="Q115" s="17">
         <v>9.6759259259259253E-2</v>
       </c>
-      <c r="R115" s="20">
+      <c r="R115" s="17">
         <v>53.617366412213734</v>
       </c>
-      <c r="S115" s="20">
+      <c r="S115" s="17">
         <v>98.694444444444443</v>
       </c>
-      <c r="T115" s="20">
+      <c r="T115" s="17">
         <v>152.31181085665818</v>
       </c>
     </row>
@@ -5955,25 +6061,25 @@
         <v>53.8</v>
       </c>
       <c r="M116" s="1"/>
-      <c r="N116" s="19">
+      <c r="N116" s="17">
         <v>0.2625954198473282</v>
       </c>
-      <c r="O116" s="19">
+      <c r="O116" s="17">
         <v>0.39333333333333331</v>
       </c>
-      <c r="P116" s="20">
-        <v>0</v>
-      </c>
-      <c r="Q116" s="20">
-        <v>0</v>
-      </c>
-      <c r="R116" s="20">
-        <v>0</v>
-      </c>
-      <c r="S116" s="20">
-        <v>0</v>
-      </c>
-      <c r="T116" s="20">
+      <c r="P116" s="17">
+        <v>0</v>
+      </c>
+      <c r="Q116" s="17">
+        <v>0</v>
+      </c>
+      <c r="R116" s="17">
+        <v>0</v>
+      </c>
+      <c r="S116" s="17">
+        <v>0</v>
+      </c>
+      <c r="T116" s="17">
         <v>0</v>
       </c>
     </row>
@@ -6013,25 +6119,25 @@
         <v>56.8</v>
       </c>
       <c r="M117" s="1"/>
-      <c r="N117" s="19">
+      <c r="N117" s="17">
         <v>0.26145038167938928</v>
       </c>
-      <c r="O117" s="19">
+      <c r="O117" s="17">
         <v>0.39185185185185184</v>
       </c>
-      <c r="P117" s="20">
-        <v>0</v>
-      </c>
-      <c r="Q117" s="20">
-        <v>0</v>
-      </c>
-      <c r="R117" s="20">
-        <v>0</v>
-      </c>
-      <c r="S117" s="20">
-        <v>0</v>
-      </c>
-      <c r="T117" s="20">
+      <c r="P117" s="17">
+        <v>0</v>
+      </c>
+      <c r="Q117" s="17">
+        <v>0</v>
+      </c>
+      <c r="R117" s="17">
+        <v>0</v>
+      </c>
+      <c r="S117" s="17">
+        <v>0</v>
+      </c>
+      <c r="T117" s="17">
         <v>0</v>
       </c>
     </row>
@@ -6071,25 +6177,25 @@
         <v>57.7</v>
       </c>
       <c r="M118" s="1"/>
-      <c r="N118" s="19">
+      <c r="N118" s="17">
         <v>0.26030534351145035</v>
       </c>
-      <c r="O118" s="19">
+      <c r="O118" s="17">
         <v>0.39037037037037031</v>
       </c>
-      <c r="P118" s="20">
-        <v>0</v>
-      </c>
-      <c r="Q118" s="20">
-        <v>0</v>
-      </c>
-      <c r="R118" s="20">
-        <v>0</v>
-      </c>
-      <c r="S118" s="20">
-        <v>0</v>
-      </c>
-      <c r="T118" s="20">
+      <c r="P118" s="17">
+        <v>0</v>
+      </c>
+      <c r="Q118" s="17">
+        <v>0</v>
+      </c>
+      <c r="R118" s="17">
+        <v>0</v>
+      </c>
+      <c r="S118" s="17">
+        <v>0</v>
+      </c>
+      <c r="T118" s="17">
         <v>0</v>
       </c>
     </row>
@@ -6129,25 +6235,25 @@
         <v>60.3</v>
       </c>
       <c r="M119" s="1"/>
-      <c r="N119" s="19">
+      <c r="N119" s="17">
         <v>0.25954198473282442</v>
       </c>
-      <c r="O119" s="19">
+      <c r="O119" s="17">
         <v>0.38851851851851849</v>
       </c>
-      <c r="P119" s="20">
-        <v>0</v>
-      </c>
-      <c r="Q119" s="20">
-        <v>0</v>
-      </c>
-      <c r="R119" s="20">
-        <v>0</v>
-      </c>
-      <c r="S119" s="20">
-        <v>0</v>
-      </c>
-      <c r="T119" s="20">
+      <c r="P119" s="17">
+        <v>0</v>
+      </c>
+      <c r="Q119" s="17">
+        <v>0</v>
+      </c>
+      <c r="R119" s="17">
+        <v>0</v>
+      </c>
+      <c r="S119" s="17">
+        <v>0</v>
+      </c>
+      <c r="T119" s="17">
         <v>0</v>
       </c>
     </row>
@@ -6187,25 +6293,25 @@
         <v>59.7</v>
       </c>
       <c r="M120" s="1"/>
-      <c r="N120" s="19">
+      <c r="N120" s="17">
         <v>0.25839694656488549</v>
       </c>
-      <c r="O120" s="19">
+      <c r="O120" s="17">
         <v>0.38703703703703701</v>
       </c>
-      <c r="P120" s="20">
-        <v>0</v>
-      </c>
-      <c r="Q120" s="20">
-        <v>0</v>
-      </c>
-      <c r="R120" s="20">
-        <v>0</v>
-      </c>
-      <c r="S120" s="20">
-        <v>0</v>
-      </c>
-      <c r="T120" s="20">
+      <c r="P120" s="17">
+        <v>0</v>
+      </c>
+      <c r="Q120" s="17">
+        <v>0</v>
+      </c>
+      <c r="R120" s="17">
+        <v>0</v>
+      </c>
+      <c r="S120" s="17">
+        <v>0</v>
+      </c>
+      <c r="T120" s="17">
         <v>0</v>
       </c>
     </row>
@@ -6245,25 +6351,25 @@
         <v>47</v>
       </c>
       <c r="M121" s="1"/>
-      <c r="N121" s="19">
+      <c r="N121" s="17">
         <v>0.2625954198473282</v>
       </c>
-      <c r="O121" s="19">
+      <c r="O121" s="17">
         <v>0.39333333333333331</v>
       </c>
-      <c r="P121" s="20">
+      <c r="P121" s="17">
         <v>3.2824427480916026E-3</v>
       </c>
-      <c r="Q121" s="20">
+      <c r="Q121" s="17">
         <v>4.9166666666666664E-3</v>
       </c>
-      <c r="R121" s="20">
+      <c r="R121" s="17">
         <v>2.72442748091603</v>
       </c>
-      <c r="S121" s="20">
+      <c r="S121" s="17">
         <v>5.0149999999999997</v>
       </c>
-      <c r="T121" s="20">
+      <c r="T121" s="17">
         <v>7.7394274809160297</v>
       </c>
     </row>
@@ -6303,25 +6409,25 @@
         <v>50.2</v>
       </c>
       <c r="M122" s="1"/>
-      <c r="N122" s="19">
+      <c r="N122" s="17">
         <v>0.26145038167938928</v>
       </c>
-      <c r="O122" s="19">
+      <c r="O122" s="17">
         <v>0.39185185185185184</v>
       </c>
-      <c r="P122" s="20">
+      <c r="P122" s="17">
         <v>3.2681297709923661E-3</v>
       </c>
-      <c r="Q122" s="20">
+      <c r="Q122" s="17">
         <v>4.898148148148148E-3</v>
       </c>
-      <c r="R122" s="20">
+      <c r="R122" s="17">
         <v>2.7125477099236637</v>
       </c>
-      <c r="S122" s="20">
+      <c r="S122" s="17">
         <v>4.9961111111111105</v>
       </c>
-      <c r="T122" s="20">
+      <c r="T122" s="17">
         <v>7.7086588210347742</v>
       </c>
     </row>
@@ -6361,25 +6467,25 @@
         <v>52.5</v>
       </c>
       <c r="M123" s="1"/>
-      <c r="N123" s="19">
+      <c r="N123" s="17">
         <v>0.26030534351145035</v>
       </c>
-      <c r="O123" s="19">
+      <c r="O123" s="17">
         <v>0.39037037037037031</v>
       </c>
-      <c r="P123" s="20">
+      <c r="P123" s="17">
         <v>3.2538167938931297E-3</v>
       </c>
-      <c r="Q123" s="20">
+      <c r="Q123" s="17">
         <v>4.8796296296296287E-3</v>
       </c>
-      <c r="R123" s="20">
+      <c r="R123" s="17">
         <v>2.7006679389312978</v>
       </c>
-      <c r="S123" s="20">
+      <c r="S123" s="17">
         <v>4.9772222222222213</v>
       </c>
-      <c r="T123" s="20">
+      <c r="T123" s="17">
         <v>7.6778901611535186</v>
       </c>
     </row>
@@ -6419,25 +6525,25 @@
         <v>55.4</v>
       </c>
       <c r="M124" s="1"/>
-      <c r="N124" s="19">
+      <c r="N124" s="17">
         <v>0.25954198473282442</v>
       </c>
-      <c r="O124" s="19">
+      <c r="O124" s="17">
         <v>0.38851851851851849</v>
       </c>
-      <c r="P124" s="20">
+      <c r="P124" s="17">
         <v>3.2442748091603053E-3</v>
       </c>
-      <c r="Q124" s="20">
+      <c r="Q124" s="17">
         <v>4.8564814814814807E-3</v>
       </c>
-      <c r="R124" s="20">
+      <c r="R124" s="17">
         <v>2.6927480916030531</v>
       </c>
-      <c r="S124" s="20">
+      <c r="S124" s="17">
         <v>4.9536111111111101</v>
       </c>
-      <c r="T124" s="20">
+      <c r="T124" s="17">
         <v>7.6463592027141631</v>
       </c>
     </row>
@@ -6477,25 +6583,25 @@
         <v>56.4</v>
       </c>
       <c r="M125" s="1"/>
-      <c r="N125" s="19">
+      <c r="N125" s="17">
         <v>0.25839694656488549</v>
       </c>
-      <c r="O125" s="19">
+      <c r="O125" s="17">
         <v>0.38703703703703701</v>
       </c>
-      <c r="P125" s="20">
+      <c r="P125" s="17">
         <v>3.2299618320610684E-3</v>
       </c>
-      <c r="Q125" s="20">
+      <c r="Q125" s="17">
         <v>4.8379629629629632E-3</v>
       </c>
-      <c r="R125" s="20">
+      <c r="R125" s="17">
         <v>2.6808683206106867</v>
       </c>
-      <c r="S125" s="20">
+      <c r="S125" s="17">
         <v>4.9347222222222227</v>
       </c>
-      <c r="T125" s="20">
+      <c r="T125" s="17">
         <v>7.6155905428329094</v>
       </c>
     </row>
@@ -6535,25 +6641,25 @@
         <v>41.5</v>
       </c>
       <c r="M126" s="1"/>
-      <c r="N126" s="19">
+      <c r="N126" s="17">
         <v>0.2625954198473282</v>
       </c>
-      <c r="O126" s="19">
+      <c r="O126" s="17">
         <v>0.39333333333333331</v>
       </c>
-      <c r="P126" s="20">
+      <c r="P126" s="17">
         <v>6.5648854961832051E-3</v>
       </c>
-      <c r="Q126" s="20">
+      <c r="Q126" s="17">
         <v>9.8333333333333328E-3</v>
       </c>
-      <c r="R126" s="20">
+      <c r="R126" s="17">
         <v>5.4488549618320601</v>
       </c>
-      <c r="S126" s="20">
+      <c r="S126" s="17">
         <v>10.029999999999999</v>
       </c>
-      <c r="T126" s="20">
+      <c r="T126" s="17">
         <v>15.478854961832059</v>
       </c>
     </row>
@@ -6593,25 +6699,25 @@
         <v>43.1</v>
       </c>
       <c r="M127" s="1"/>
-      <c r="N127" s="19">
+      <c r="N127" s="17">
         <v>0.26145038167938928</v>
       </c>
-      <c r="O127" s="19">
+      <c r="O127" s="17">
         <v>0.39185185185185184</v>
       </c>
-      <c r="P127" s="20">
+      <c r="P127" s="17">
         <v>6.5362595419847323E-3</v>
       </c>
-      <c r="Q127" s="20">
+      <c r="Q127" s="17">
         <v>9.796296296296296E-3</v>
       </c>
-      <c r="R127" s="20">
+      <c r="R127" s="17">
         <v>5.4250954198473273</v>
       </c>
-      <c r="S127" s="20">
+      <c r="S127" s="17">
         <v>9.992222222222221</v>
       </c>
-      <c r="T127" s="20">
+      <c r="T127" s="17">
         <v>15.417317642069548</v>
       </c>
     </row>
@@ -6651,25 +6757,25 @@
         <v>46.1</v>
       </c>
       <c r="M128" s="1"/>
-      <c r="N128" s="19">
+      <c r="N128" s="17">
         <v>0.26030534351145035</v>
       </c>
-      <c r="O128" s="19">
+      <c r="O128" s="17">
         <v>0.39037037037037031</v>
       </c>
-      <c r="P128" s="20">
+      <c r="P128" s="17">
         <v>6.5076335877862594E-3</v>
       </c>
-      <c r="Q128" s="20">
+      <c r="Q128" s="17">
         <v>9.7592592592592575E-3</v>
       </c>
-      <c r="R128" s="20">
+      <c r="R128" s="17">
         <v>5.4013358778625955</v>
       </c>
-      <c r="S128" s="20">
+      <c r="S128" s="17">
         <v>9.9544444444444427</v>
       </c>
-      <c r="T128" s="20">
+      <c r="T128" s="17">
         <v>15.355780322307037</v>
       </c>
     </row>
@@ -6709,25 +6815,25 @@
         <v>49.3</v>
       </c>
       <c r="M129" s="1"/>
-      <c r="N129" s="19">
+      <c r="N129" s="17">
         <v>0.25954198473282442</v>
       </c>
-      <c r="O129" s="19">
+      <c r="O129" s="17">
         <v>0.38851851851851849</v>
       </c>
-      <c r="P129" s="20">
+      <c r="P129" s="17">
         <v>6.4885496183206106E-3</v>
       </c>
-      <c r="Q129" s="20">
+      <c r="Q129" s="17">
         <v>9.7129629629629614E-3</v>
       </c>
-      <c r="R129" s="20">
+      <c r="R129" s="17">
         <v>5.3854961832061061</v>
       </c>
-      <c r="S129" s="20">
+      <c r="S129" s="17">
         <v>9.9072222222222202</v>
       </c>
-      <c r="T129" s="20">
+      <c r="T129" s="17">
         <v>15.292718405428326</v>
       </c>
     </row>
@@ -6767,25 +6873,25 @@
         <v>51.3</v>
       </c>
       <c r="M130" s="1"/>
-      <c r="N130" s="19">
+      <c r="N130" s="17">
         <v>0.25839694656488549</v>
       </c>
-      <c r="O130" s="19">
+      <c r="O130" s="17">
         <v>0.38703703703703701</v>
       </c>
-      <c r="P130" s="20">
+      <c r="P130" s="17">
         <v>6.4599236641221369E-3</v>
       </c>
-      <c r="Q130" s="20">
+      <c r="Q130" s="17">
         <v>9.6759259259259264E-3</v>
       </c>
-      <c r="R130" s="20">
+      <c r="R130" s="17">
         <v>5.3617366412213734</v>
       </c>
-      <c r="S130" s="20">
+      <c r="S130" s="17">
         <v>9.8694444444444454</v>
       </c>
-      <c r="T130" s="20">
+      <c r="T130" s="17">
         <v>15.231181085665819</v>
       </c>
     </row>
@@ -6825,25 +6931,25 @@
         <v>31.8</v>
       </c>
       <c r="M131" s="1"/>
-      <c r="N131" s="19">
+      <c r="N131" s="17">
         <v>0.2625954198473282</v>
       </c>
-      <c r="O131" s="19">
+      <c r="O131" s="17">
         <v>0.39333333333333331</v>
       </c>
-      <c r="P131" s="20">
+      <c r="P131" s="17">
         <v>1.312977099236641E-2</v>
       </c>
-      <c r="Q131" s="20">
+      <c r="Q131" s="17">
         <v>1.9666666666666666E-2</v>
       </c>
-      <c r="R131" s="20">
+      <c r="R131" s="17">
         <v>10.89770992366412</v>
       </c>
-      <c r="S131" s="20">
+      <c r="S131" s="17">
         <v>20.059999999999999</v>
       </c>
-      <c r="T131" s="20">
+      <c r="T131" s="17">
         <v>30.957709923664119</v>
       </c>
     </row>
@@ -6883,25 +6989,25 @@
         <v>35.799999999999997</v>
       </c>
       <c r="M132" s="1"/>
-      <c r="N132" s="19">
+      <c r="N132" s="17">
         <v>0.26145038167938928</v>
       </c>
-      <c r="O132" s="19">
+      <c r="O132" s="17">
         <v>0.39185185185185184</v>
       </c>
-      <c r="P132" s="20">
+      <c r="P132" s="17">
         <v>1.3072519083969465E-2</v>
       </c>
-      <c r="Q132" s="20">
+      <c r="Q132" s="17">
         <v>1.9592592592592592E-2</v>
       </c>
-      <c r="R132" s="20">
+      <c r="R132" s="17">
         <v>10.850190839694655</v>
       </c>
-      <c r="S132" s="20">
+      <c r="S132" s="17">
         <v>19.984444444444442</v>
       </c>
-      <c r="T132" s="20">
+      <c r="T132" s="17">
         <v>30.834635284139097</v>
       </c>
     </row>
@@ -6941,25 +7047,25 @@
         <v>37.6</v>
       </c>
       <c r="M133" s="1"/>
-      <c r="N133" s="19">
+      <c r="N133" s="17">
         <v>0.26030534351145035</v>
       </c>
-      <c r="O133" s="19">
+      <c r="O133" s="17">
         <v>0.39037037037037031</v>
       </c>
-      <c r="P133" s="20">
+      <c r="P133" s="17">
         <v>1.3015267175572519E-2</v>
       </c>
-      <c r="Q133" s="20">
+      <c r="Q133" s="17">
         <v>1.9518518518518515E-2</v>
       </c>
-      <c r="R133" s="20">
+      <c r="R133" s="17">
         <v>10.802671755725191</v>
       </c>
-      <c r="S133" s="20">
+      <c r="S133" s="17">
         <v>19.908888888888885</v>
       </c>
-      <c r="T133" s="20">
+      <c r="T133" s="17">
         <v>30.711560644614075</v>
       </c>
     </row>
@@ -6999,25 +7105,25 @@
         <v>41.3</v>
       </c>
       <c r="M134" s="1"/>
-      <c r="N134" s="19">
+      <c r="N134" s="17">
         <v>0.25954198473282442</v>
       </c>
-      <c r="O134" s="19">
+      <c r="O134" s="17">
         <v>0.38851851851851849</v>
       </c>
-      <c r="P134" s="20">
+      <c r="P134" s="17">
         <v>1.2977099236641221E-2</v>
       </c>
-      <c r="Q134" s="20">
+      <c r="Q134" s="17">
         <v>1.9425925925925923E-2</v>
       </c>
-      <c r="R134" s="20">
+      <c r="R134" s="17">
         <v>10.770992366412212</v>
       </c>
-      <c r="S134" s="20">
+      <c r="S134" s="17">
         <v>19.81444444444444</v>
       </c>
-      <c r="T134" s="20">
+      <c r="T134" s="17">
         <v>30.585436810856653</v>
       </c>
     </row>
@@ -7057,25 +7163,25 @@
         <v>41.2</v>
       </c>
       <c r="M135" s="1"/>
-      <c r="N135" s="19">
+      <c r="N135" s="17">
         <v>0.25839694656488549</v>
       </c>
-      <c r="O135" s="19">
+      <c r="O135" s="17">
         <v>0.38703703703703701</v>
       </c>
-      <c r="P135" s="20">
+      <c r="P135" s="17">
         <v>1.2919847328244274E-2</v>
       </c>
-      <c r="Q135" s="20">
+      <c r="Q135" s="17">
         <v>1.9351851851851853E-2</v>
       </c>
-      <c r="R135" s="20">
+      <c r="R135" s="17">
         <v>10.723473282442747</v>
       </c>
-      <c r="S135" s="20">
+      <c r="S135" s="17">
         <v>19.738888888888891</v>
       </c>
-      <c r="T135" s="20">
+      <c r="T135" s="17">
         <v>30.462362171331637</v>
       </c>
     </row>
@@ -7115,25 +7221,25 @@
         <v>24.3</v>
       </c>
       <c r="M136" s="1"/>
-      <c r="N136" s="19">
+      <c r="N136" s="17">
         <v>0.2625954198473282</v>
       </c>
-      <c r="O136" s="19">
+      <c r="O136" s="17">
         <v>0.39333333333333331</v>
       </c>
-      <c r="P136" s="20">
+      <c r="P136" s="17">
         <v>1.9694656488549615E-2</v>
       </c>
-      <c r="Q136" s="20">
+      <c r="Q136" s="17">
         <v>2.9499999999999998E-2</v>
       </c>
-      <c r="R136" s="20">
+      <c r="R136" s="17">
         <v>16.346564885496182</v>
       </c>
-      <c r="S136" s="20">
+      <c r="S136" s="17">
         <v>30.09</v>
       </c>
-      <c r="T136" s="20">
+      <c r="T136" s="17">
         <v>46.436564885496182</v>
       </c>
     </row>
@@ -7173,25 +7279,25 @@
         <v>28.8</v>
       </c>
       <c r="M137" s="1"/>
-      <c r="N137" s="19">
+      <c r="N137" s="17">
         <v>0.26145038167938928</v>
       </c>
-      <c r="O137" s="19">
+      <c r="O137" s="17">
         <v>0.39185185185185184</v>
       </c>
-      <c r="P137" s="20">
+      <c r="P137" s="17">
         <v>1.9608778625954195E-2</v>
       </c>
-      <c r="Q137" s="20">
+      <c r="Q137" s="17">
         <v>2.9388888888888888E-2</v>
       </c>
-      <c r="R137" s="20">
+      <c r="R137" s="17">
         <v>16.275286259541982</v>
       </c>
-      <c r="S137" s="20">
+      <c r="S137" s="17">
         <v>29.976666666666667</v>
       </c>
-      <c r="T137" s="20">
+      <c r="T137" s="17">
         <v>46.251952926208645</v>
       </c>
     </row>
@@ -7231,25 +7337,25 @@
         <v>31.4</v>
       </c>
       <c r="M138" s="1"/>
-      <c r="N138" s="19">
+      <c r="N138" s="17">
         <v>0.26030534351145035</v>
       </c>
-      <c r="O138" s="19">
+      <c r="O138" s="17">
         <v>0.39037037037037031</v>
       </c>
-      <c r="P138" s="20">
+      <c r="P138" s="17">
         <v>1.9522900763358778E-2</v>
       </c>
-      <c r="Q138" s="20">
+      <c r="Q138" s="17">
         <v>2.9277777777777771E-2</v>
       </c>
-      <c r="R138" s="20">
+      <c r="R138" s="17">
         <v>16.204007633587786</v>
       </c>
-      <c r="S138" s="20">
+      <c r="S138" s="17">
         <v>29.863333333333326</v>
       </c>
-      <c r="T138" s="20">
+      <c r="T138" s="17">
         <v>46.067340966921108</v>
       </c>
     </row>
@@ -7289,25 +7395,25 @@
         <v>32.799999999999997</v>
       </c>
       <c r="M139" s="1"/>
-      <c r="N139" s="19">
+      <c r="N139" s="17">
         <v>0.25954198473282442</v>
       </c>
-      <c r="O139" s="19">
+      <c r="O139" s="17">
         <v>0.38851851851851849</v>
       </c>
-      <c r="P139" s="20">
+      <c r="P139" s="17">
         <v>1.9465648854961829E-2</v>
       </c>
-      <c r="Q139" s="20">
+      <c r="Q139" s="17">
         <v>2.9138888888888888E-2</v>
       </c>
-      <c r="R139" s="20">
+      <c r="R139" s="17">
         <v>16.156488549618317</v>
       </c>
-      <c r="S139" s="20">
+      <c r="S139" s="17">
         <v>29.721666666666668</v>
       </c>
-      <c r="T139" s="20">
+      <c r="T139" s="17">
         <v>45.878155216284981</v>
       </c>
     </row>
@@ -7347,25 +7453,25 @@
         <v>34.200000000000003</v>
       </c>
       <c r="M140" s="1"/>
-      <c r="N140" s="19">
+      <c r="N140" s="17">
         <v>0.25839694656488549</v>
       </c>
-      <c r="O140" s="19">
+      <c r="O140" s="17">
         <v>0.38703703703703701</v>
       </c>
-      <c r="P140" s="20">
+      <c r="P140" s="17">
         <v>1.9379770992366412E-2</v>
       </c>
-      <c r="Q140" s="20">
+      <c r="Q140" s="17">
         <v>2.9027777777777777E-2</v>
       </c>
-      <c r="R140" s="20">
+      <c r="R140" s="17">
         <v>16.08520992366412</v>
       </c>
-      <c r="S140" s="20">
+      <c r="S140" s="17">
         <v>29.608333333333334</v>
       </c>
-      <c r="T140" s="20">
+      <c r="T140" s="17">
         <v>45.693543256997458</v>
       </c>
     </row>
@@ -7405,25 +7511,25 @@
         <v>16.2</v>
       </c>
       <c r="M141" s="1"/>
-      <c r="N141" s="19">
+      <c r="N141" s="17">
         <v>0.2625954198473282</v>
       </c>
-      <c r="O141" s="19">
+      <c r="O141" s="17">
         <v>0.39333333333333331</v>
       </c>
-      <c r="P141" s="20">
+      <c r="P141" s="17">
         <v>3.2824427480916026E-2</v>
       </c>
-      <c r="Q141" s="20">
+      <c r="Q141" s="17">
         <v>4.9166666666666664E-2</v>
       </c>
-      <c r="R141" s="20">
+      <c r="R141" s="17">
         <v>27.244274809160299</v>
       </c>
-      <c r="S141" s="20">
+      <c r="S141" s="17">
         <v>50.15</v>
       </c>
-      <c r="T141" s="20">
+      <c r="T141" s="17">
         <v>77.394274809160294</v>
       </c>
     </row>
@@ -7463,25 +7569,25 @@
         <v>18.2</v>
       </c>
       <c r="M142" s="1"/>
-      <c r="N142" s="19">
+      <c r="N142" s="17">
         <v>0.26145038167938928</v>
       </c>
-      <c r="O142" s="19">
+      <c r="O142" s="17">
         <v>0.39185185185185184</v>
       </c>
-      <c r="P142" s="20">
+      <c r="P142" s="17">
         <v>3.268129770992366E-2</v>
       </c>
-      <c r="Q142" s="20">
+      <c r="Q142" s="17">
         <v>4.898148148148148E-2</v>
       </c>
-      <c r="R142" s="20">
+      <c r="R142" s="17">
         <v>27.125477099236633</v>
       </c>
-      <c r="S142" s="20">
+      <c r="S142" s="17">
         <v>49.961111111111109</v>
       </c>
-      <c r="T142" s="20">
+      <c r="T142" s="17">
         <v>77.086588210347742</v>
       </c>
     </row>
@@ -7521,25 +7627,25 @@
         <v>20.100000000000001</v>
       </c>
       <c r="M143" s="1"/>
-      <c r="N143" s="19">
+      <c r="N143" s="17">
         <v>0.26030534351145035</v>
       </c>
-      <c r="O143" s="19">
+      <c r="O143" s="17">
         <v>0.39037037037037031</v>
       </c>
-      <c r="P143" s="20">
+      <c r="P143" s="17">
         <v>3.2538167938931294E-2</v>
       </c>
-      <c r="Q143" s="20">
+      <c r="Q143" s="17">
         <v>4.8796296296296289E-2</v>
       </c>
-      <c r="R143" s="20">
+      <c r="R143" s="17">
         <v>27.006679389312971</v>
       </c>
-      <c r="S143" s="20">
+      <c r="S143" s="17">
         <v>49.772222222222219</v>
       </c>
-      <c r="T143" s="20">
+      <c r="T143" s="17">
         <v>76.77890161153519</v>
       </c>
     </row>
@@ -7579,25 +7685,25 @@
         <v>21.2</v>
       </c>
       <c r="M144" s="1"/>
-      <c r="N144" s="19">
+      <c r="N144" s="17">
         <v>0.25954198473282442</v>
       </c>
-      <c r="O144" s="19">
+      <c r="O144" s="17">
         <v>0.38851851851851849</v>
       </c>
-      <c r="P144" s="20">
+      <c r="P144" s="17">
         <v>3.2442748091603052E-2</v>
       </c>
-      <c r="Q144" s="20">
+      <c r="Q144" s="17">
         <v>4.8564814814814811E-2</v>
       </c>
-      <c r="R144" s="20">
+      <c r="R144" s="17">
         <v>26.927480916030532</v>
       </c>
-      <c r="S144" s="20">
+      <c r="S144" s="17">
         <v>49.536111111111104</v>
       </c>
-      <c r="T144" s="20">
+      <c r="T144" s="17">
         <v>76.46359202714163</v>
       </c>
     </row>
@@ -7637,25 +7743,25 @@
         <v>23.1</v>
       </c>
       <c r="M145" s="1"/>
-      <c r="N145" s="19">
+      <c r="N145" s="17">
         <v>0.25839694656488549</v>
       </c>
-      <c r="O145" s="19">
+      <c r="O145" s="17">
         <v>0.38703703703703701</v>
       </c>
-      <c r="P145" s="20">
+      <c r="P145" s="17">
         <v>3.2299618320610686E-2</v>
       </c>
-      <c r="Q145" s="20">
+      <c r="Q145" s="17">
         <v>4.8379629629629627E-2</v>
       </c>
-      <c r="R145" s="20">
+      <c r="R145" s="17">
         <v>26.808683206106867</v>
       </c>
-      <c r="S145" s="20">
+      <c r="S145" s="17">
         <v>49.347222222222221</v>
       </c>
-      <c r="T145" s="20">
+      <c r="T145" s="17">
         <v>76.155905428329092</v>
       </c>
     </row>
@@ -7695,25 +7801,25 @@
         <v>7.1</v>
       </c>
       <c r="M146" s="1"/>
-      <c r="N146" s="19">
+      <c r="N146" s="17">
         <v>0.2625954198473282</v>
       </c>
-      <c r="O146" s="19">
+      <c r="O146" s="17">
         <v>0.39333333333333331</v>
       </c>
-      <c r="P146" s="20">
+      <c r="P146" s="17">
         <v>6.5648854961832051E-2</v>
       </c>
-      <c r="Q146" s="20">
+      <c r="Q146" s="17">
         <v>9.8333333333333328E-2</v>
       </c>
-      <c r="R146" s="20">
+      <c r="R146" s="17">
         <v>54.488549618320597</v>
       </c>
-      <c r="S146" s="20">
+      <c r="S146" s="17">
         <v>100.3</v>
       </c>
-      <c r="T146" s="20">
+      <c r="T146" s="17">
         <v>154.78854961832059</v>
       </c>
     </row>
@@ -7753,25 +7859,25 @@
         <v>7.2</v>
       </c>
       <c r="M147" s="1"/>
-      <c r="N147" s="19">
+      <c r="N147" s="17">
         <v>0.26145038167938928</v>
       </c>
-      <c r="O147" s="19">
+      <c r="O147" s="17">
         <v>0.39185185185185184</v>
       </c>
-      <c r="P147" s="20">
+      <c r="P147" s="17">
         <v>6.5362595419847319E-2</v>
       </c>
-      <c r="Q147" s="20">
+      <c r="Q147" s="17">
         <v>9.796296296296296E-2</v>
       </c>
-      <c r="R147" s="20">
+      <c r="R147" s="17">
         <v>54.250954198473266</v>
       </c>
-      <c r="S147" s="20">
+      <c r="S147" s="17">
         <v>99.922222222222217</v>
       </c>
-      <c r="T147" s="20">
+      <c r="T147" s="17">
         <v>154.17317642069548</v>
       </c>
     </row>
@@ -7811,25 +7917,25 @@
         <v>8.1</v>
       </c>
       <c r="M148" s="1"/>
-      <c r="N148" s="19">
+      <c r="N148" s="17">
         <v>0.26030534351145035</v>
       </c>
-      <c r="O148" s="19">
+      <c r="O148" s="17">
         <v>0.39037037037037031</v>
       </c>
-      <c r="P148" s="20">
+      <c r="P148" s="17">
         <v>6.5076335877862587E-2</v>
       </c>
-      <c r="Q148" s="20">
+      <c r="Q148" s="17">
         <v>9.7592592592592578E-2</v>
       </c>
-      <c r="R148" s="20">
+      <c r="R148" s="17">
         <v>54.013358778625943</v>
       </c>
-      <c r="S148" s="20">
+      <c r="S148" s="17">
         <v>99.544444444444437</v>
       </c>
-      <c r="T148" s="20">
+      <c r="T148" s="17">
         <v>153.55780322307038</v>
       </c>
     </row>
@@ -7869,25 +7975,25 @@
         <v>8.4</v>
       </c>
       <c r="M149" s="1"/>
-      <c r="N149" s="19">
+      <c r="N149" s="17">
         <v>0.25954198473282442</v>
       </c>
-      <c r="O149" s="19">
+      <c r="O149" s="17">
         <v>0.38851851851851849</v>
       </c>
-      <c r="P149" s="20">
+      <c r="P149" s="17">
         <v>6.4885496183206104E-2</v>
       </c>
-      <c r="Q149" s="20">
+      <c r="Q149" s="17">
         <v>9.7129629629629621E-2</v>
       </c>
-      <c r="R149" s="20">
+      <c r="R149" s="17">
         <v>53.854961832061065</v>
       </c>
-      <c r="S149" s="20">
+      <c r="S149" s="17">
         <v>99.072222222222209</v>
       </c>
-      <c r="T149" s="20">
+      <c r="T149" s="17">
         <v>152.92718405428326</v>
       </c>
     </row>
@@ -7927,25 +8033,25 @@
         <v>8.6</v>
       </c>
       <c r="M150" s="1"/>
-      <c r="N150" s="19">
+      <c r="N150" s="17">
         <v>0.25839694656488549</v>
       </c>
-      <c r="O150" s="19">
+      <c r="O150" s="17">
         <v>0.38703703703703701</v>
       </c>
-      <c r="P150" s="20">
+      <c r="P150" s="17">
         <v>6.4599236641221372E-2</v>
       </c>
-      <c r="Q150" s="20">
+      <c r="Q150" s="17">
         <v>9.6759259259259253E-2</v>
       </c>
-      <c r="R150" s="20">
+      <c r="R150" s="17">
         <v>53.617366412213734</v>
       </c>
-      <c r="S150" s="20">
+      <c r="S150" s="17">
         <v>98.694444444444443</v>
       </c>
-      <c r="T150" s="20">
+      <c r="T150" s="17">
         <v>152.31181085665818</v>
       </c>
     </row>
@@ -8030,8 +8136,8 @@
       <c r="O152" s="1"/>
     </row>
     <row r="153" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A153" s="1" t="s">
-        <v>18</v>
+      <c r="A153" s="21" t="s">
+        <v>32</v>
       </c>
       <c r="B153" s="3">
         <v>0.4</v>
@@ -8071,7 +8177,9 @@
       <c r="O153" s="1"/>
     </row>
     <row r="154" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A154" s="1"/>
+      <c r="A154" s="21" t="s">
+        <v>33</v>
+      </c>
       <c r="B154" s="3">
         <v>0.4</v>
       </c>
@@ -8110,7 +8218,7 @@
       <c r="O154" s="1"/>
     </row>
     <row r="155" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A155" s="1"/>
+      <c r="A155" s="21"/>
       <c r="B155" s="3">
         <v>0.4</v>
       </c>
@@ -8149,6 +8257,9 @@
       <c r="O155" s="1"/>
     </row>
     <row r="156" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A156" s="21" t="s">
+        <v>35</v>
+      </c>
       <c r="B156" s="3">
         <v>0.4</v>
       </c>
@@ -8187,7 +8298,9 @@
       <c r="O156" s="1"/>
     </row>
     <row r="157" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A157" s="1"/>
+      <c r="A157" s="21" t="s">
+        <v>37</v>
+      </c>
       <c r="B157" s="3">
         <v>0.4</v>
       </c>
@@ -12099,5 +12212,6 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>